--- a/tests/testdata/excel/フォルダ/隠しファイル.xlsx
+++ b/tests/testdata/excel/フォルダ/隠しファイル.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A75F4D0F-13CA-4DBE-A44C-1614F19FA4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B27B0A4-6F13-494B-9F52-CB1F21641BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{AEE2E567-8A97-4FB8-B4D5-CBE4CBF8EB60}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{C155FFF5-B94D-4240-B9B6-1A1949320E28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3B1592F-964B-4F35-B2FF-3CB75A11909F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{217BF535-DB83-4F80-920B-1D73DB9978E0}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/フォルダ/隠しファイル.xlsx
+++ b/tests/testdata/excel/フォルダ/隠しファイル.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B27B0A4-6F13-494B-9F52-CB1F21641BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDB83531-B1DD-47CA-A190-730C9335C685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{C155FFF5-B94D-4240-B9B6-1A1949320E28}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{7484F42E-0657-4C57-B33B-BC755CF0F4B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{217BF535-DB83-4F80-920B-1D73DB9978E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C11E254B-8C5E-48F7-8EB6-5881CE53CD28}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
